--- a/CM5IO_BOM.xlsx
+++ b/CM5IO_BOM.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Elektronika Schematy\KiCad\IARC-RPi_CM5_drone_platform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA61079-F0D4-4988-8A58-AF5CA445418F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BCC745-7B35-4308-85A8-4B8745FCF21F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{2D0DF511-CD42-495F-98C8-D8FF06CCC30B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bottom" sheetId="1" r:id="rId1"/>
     <sheet name="Top" sheetId="3" r:id="rId2"/>
-    <sheet name="MOUSER ZAMÓWIENIE 1" sheetId="4" r:id="rId3"/>
+    <sheet name="MOUSER ZAMÓWIENIE" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="249">
   <si>
     <t>Ilość</t>
   </si>
@@ -804,6 +804,9 @@
   </si>
   <si>
     <t xml:space="preserve">859-LTST-S270KGKT </t>
+  </si>
+  <si>
+    <t>Aternatywa</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1494,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
@@ -1618,6 +1621,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1980,8 +1984,8 @@
     <col min="5" max="5" width="34.7109375" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" customWidth="1"/>
     <col min="7" max="7" width="9.85546875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="101" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" style="92" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="102" customWidth="1"/>
+    <col min="9" max="9" width="9.85546875" style="93" customWidth="1"/>
     <col min="10" max="10" width="30.140625" style="25" customWidth="1"/>
     <col min="11" max="11" width="9.85546875" style="10" customWidth="1"/>
     <col min="12" max="12" width="30.140625" style="11" customWidth="1"/>
@@ -2010,7 +2014,7 @@
       <c r="G1" s="81" t="s">
         <v>132</v>
       </c>
-      <c r="H1" s="98"/>
+      <c r="H1" s="99"/>
       <c r="I1" s="83" t="s">
         <v>134</v>
       </c>
@@ -2030,10 +2034,10 @@
       <c r="G2" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="H2" s="99" t="s">
+      <c r="H2" s="100" t="s">
         <v>131</v>
       </c>
-      <c r="I2" s="93" t="s">
+      <c r="I2" s="94" t="s">
         <v>121</v>
       </c>
       <c r="J2" s="51" t="s">
@@ -2069,8 +2073,8 @@
         <v>135</v>
       </c>
       <c r="G3" s="32"/>
-      <c r="H3" s="100"/>
-      <c r="I3" s="94"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="95"/>
       <c r="J3" s="35"/>
       <c r="K3" s="36">
         <v>3.9190000000000003E-2</v>
@@ -2614,8 +2618,8 @@
         <v>37</v>
       </c>
       <c r="G20" s="42"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="95"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="96"/>
       <c r="J20" s="45"/>
       <c r="K20" s="46"/>
       <c r="L20" s="47"/>
@@ -2628,8 +2632,8 @@
       <c r="E21" s="61"/>
       <c r="F21" s="62"/>
       <c r="G21" s="63"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="96"/>
+      <c r="H21" s="104"/>
+      <c r="I21" s="97"/>
       <c r="J21" s="62"/>
       <c r="K21" s="64"/>
       <c r="L21" s="65"/>
@@ -2728,8 +2732,8 @@
         <v>135</v>
       </c>
       <c r="G24" s="12"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="97"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="98"/>
       <c r="J24" s="24"/>
       <c r="K24" s="10">
         <v>2.2789999999999999</v>
@@ -2760,10 +2764,10 @@
       <c r="G25" s="13">
         <v>0.38300000000000001</v>
       </c>
-      <c r="H25" s="105" t="s">
+      <c r="H25" s="106" t="s">
         <v>246</v>
       </c>
-      <c r="I25" s="92">
+      <c r="I25" s="93">
         <v>1.65</v>
       </c>
       <c r="J25" s="56">
@@ -2798,10 +2802,10 @@
       <c r="G26" s="13">
         <v>0.30499999999999999</v>
       </c>
-      <c r="H26" s="105" t="s">
+      <c r="H26" s="106" t="s">
         <v>247</v>
       </c>
-      <c r="I26" s="92">
+      <c r="I26" s="93">
         <v>1.64</v>
       </c>
       <c r="J26" s="56">
@@ -2836,10 +2840,10 @@
       <c r="G27" s="13">
         <v>5.68</v>
       </c>
-      <c r="H27" s="105" t="s">
+      <c r="H27" s="106" t="s">
         <v>241</v>
       </c>
-      <c r="I27" s="92">
+      <c r="I27" s="93">
         <v>7.17</v>
       </c>
       <c r="J27" s="56">
@@ -2981,10 +2985,10 @@
       <c r="G32" s="13">
         <v>7.7</v>
       </c>
-      <c r="H32" s="105" t="s">
+      <c r="H32" s="106" t="s">
         <v>240</v>
       </c>
-      <c r="I32" s="92">
+      <c r="I32" s="93">
         <v>8.82</v>
       </c>
       <c r="J32" s="56">
@@ -3019,10 +3023,10 @@
       <c r="G33" s="13">
         <v>1.7</v>
       </c>
-      <c r="H33" s="105" t="s">
+      <c r="H33" s="106" t="s">
         <v>239</v>
       </c>
-      <c r="I33" s="92">
+      <c r="I33" s="93">
         <v>2.52</v>
       </c>
       <c r="J33" s="56">
@@ -3057,10 +3061,10 @@
       <c r="G34" s="13">
         <v>5.5529999999999999</v>
       </c>
-      <c r="H34" s="105" t="s">
+      <c r="H34" s="106" t="s">
         <v>244</v>
       </c>
-      <c r="I34" s="92">
+      <c r="I34" s="93">
         <v>7.43</v>
       </c>
       <c r="J34" s="56">
@@ -3147,10 +3151,10 @@
       <c r="G37" s="13">
         <v>1.04</v>
       </c>
-      <c r="H37" s="105" t="s">
+      <c r="H37" s="106" t="s">
         <v>245</v>
       </c>
-      <c r="I37" s="92">
+      <c r="I37" s="93">
         <v>1.5</v>
       </c>
       <c r="J37" s="56">
@@ -3185,10 +3189,10 @@
       <c r="G38" s="13">
         <v>1.19</v>
       </c>
-      <c r="H38" s="105" t="s">
+      <c r="H38" s="106" t="s">
         <v>238</v>
       </c>
-      <c r="I38" s="92">
+      <c r="I38" s="93">
         <v>0</v>
       </c>
       <c r="J38" s="25" t="s">
@@ -3290,7 +3294,7 @@
       <c r="H45" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="I45" s="92" cm="1">
+      <c r="I45" s="93" cm="1">
         <f t="array" ref="I45">SUM(I22:I44*A22:A44)</f>
         <v>46.980000000000004</v>
       </c>
@@ -3499,6 +3503,7 @@
     <hyperlink ref="H37" r:id="rId37" xr:uid="{D38265A8-7155-483A-A751-D36348DE3503}"/>
     <hyperlink ref="H25" r:id="rId38" xr:uid="{648F9DD1-59B7-454C-A8BD-19F2BA8224D4}"/>
     <hyperlink ref="H26" r:id="rId39" xr:uid="{DBC48131-1D65-499C-8B76-4E59D1299CE0}"/>
+    <hyperlink ref="L18" r:id="rId40" xr:uid="{09BA8893-4495-41E7-88F8-697E23A9411C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4500,13 +4505,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58753BDD-603F-4060-8AE8-940A823D2E6E}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>243</v>
       </c>
@@ -4514,83 +4519,86 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="74" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="106">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" s="107">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="74" t="s">
         <v>247</v>
       </c>
-      <c r="B3" s="106">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="107">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="74" t="s">
         <v>241</v>
       </c>
-      <c r="B4" s="106">
+      <c r="B4" s="107">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="74" t="s">
         <v>240</v>
       </c>
-      <c r="B5" s="106">
+      <c r="B5" s="107">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="74" t="s">
         <v>239</v>
       </c>
-      <c r="B6" s="106">
+      <c r="B6" s="107">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="74" t="s">
         <v>244</v>
       </c>
-      <c r="B7" s="106">
+      <c r="B7" s="107">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="B8" s="106">
+      <c r="B8" s="107">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="74" t="s">
         <v>238</v>
       </c>
-      <c r="B9" s="106">
+      <c r="B9" s="107">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="74" t="s">
         <v>237</v>
       </c>
-      <c r="B10" s="106">
+      <c r="B10" s="107">
         <v>12</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E10" s="92" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="74" t="s">
         <v>242</v>
       </c>
-      <c r="B11" s="106">
+      <c r="B11" s="107">
         <v>14</v>
       </c>
     </row>
@@ -4606,6 +4614,7 @@
     <hyperlink ref="A3" r:id="rId8" xr:uid="{878A7467-6179-4A24-8C7C-A3FF18669F9E}"/>
     <hyperlink ref="A10" r:id="rId9" display="Wio-SX1262 " xr:uid="{2F1C45C3-8186-493A-A720-6D54E336F203}"/>
     <hyperlink ref="A11" r:id="rId10" xr:uid="{F7565900-56CA-4D3D-AD5A-A50CDC83F884}"/>
+    <hyperlink ref="E10" r:id="rId11" display="https://www.seeedstudio.com/Wio-SX1262-Wireless-Module-p-5981.html" xr:uid="{5FFD0F89-75BC-4585-9D7D-E4C46CD52C5E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
